--- a/_reserve2/予約システム_レスポンシブ対応_テスト仕様書.xlsx
+++ b/_reserve2/予約システム_レスポンシブ対応_テスト仕様書.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" r:id="R5ee1ad2afae64acb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A_表示・レスポンシブ" sheetId="2" r:id="Re3f4273dc71340cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C_機能回帰" sheetId="3" r:id="R9130941d62d9416e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="不具合一覧" sheetId="4" r:id="R733a10965d014657"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" r:id="R117b4b5e52f04d78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A_表示・レスポンシブ" sheetId="2" r:id="Ra5fb38d0c9a94eb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C_機能回帰" sheetId="3" r:id="Rd11d89883b6941d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="不具合一覧" sheetId="4" r:id="R094d9d4f96664560"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2589,7 +2589,7 @@
         <x:v>合格</x:v>
       </x:c>
       <x:c r="I55" s="7" t="str">
-        <x:v>Edge??????????????375px???headerRect.width=351.33, right=363.33, innerWidth=375?????????????: A_index_WinEdge_375_20260615.png / edge_loggedin_metrics_20260615.json</x:v>
+        <x:v>Edge 実機で 375px 表示を確認。ヘッダー画像はコンテナ幅内に収まり、画面幅を突き破らない。evidence: A_index_WinEdge_375_20260615.png / edge_loggedin_metrics_20260615.json</x:v>
       </x:c>
       <x:c r="J55" s="6" t="str">
         <x:v>Codex</x:v>
@@ -2624,7 +2624,7 @@
         <x:v>合格</x:v>
       </x:c>
       <x:c r="I56" s="7" t="str">
-        <x:v>Edge??????????????375px????????2?????????????????: A_index_WinEdge_375_20260615.png</x:v>
+        <x:v>Edge 実機で 375px 表示を確認。パンくずは 2 行で自然に折り返し、重なりなし。evidence: A_index_WinEdge_375_20260615.png</x:v>
       </x:c>
       <x:c r="J56" s="6" t="str">
         <x:v>Codex</x:v>
@@ -2659,7 +2659,7 @@
         <x:v>合格</x:v>
       </x:c>
       <x:c r="I57" s="7" t="str">
-        <x:v>Edge??????????????375px/1280px???????????????????????????????: A_index_WinEdge_375_20260615.png / A_index_WinEdge_1280_20260615.png</x:v>
+        <x:v>Edge 実機で 375px / 1280px 表示を確認。ボタン列のはみ出しや崩れなし。evidence: A_index_WinEdge_375_20260615.png / A_index_WinEdge_1280_20260615.png</x:v>
       </x:c>
       <x:c r="J57" s="6" t="str">
         <x:v>Codex</x:v>
@@ -2799,7 +2799,7 @@
         <x:v>合格</x:v>
       </x:c>
       <x:c r="I61" s="7" t="str">
-        <x:v>Edge??????????????375px/1280px?????Shift_JIS???????????????: A_index_WinEdge_375_20260615.png / A_index_WinEdge_1280_20260615.png</x:v>
+        <x:v>Edge 実機で 375px / 1280px 表示を確認。Shift_JIS の日本語表示に文字化けなし。evidence: A_index_WinEdge_375_20260615.png / A_index_WinEdge_1280_20260615.png</x:v>
       </x:c>
       <x:c r="J61" s="6" t="str">
         <x:v>Codex</x:v>
@@ -5701,10 +5701,10 @@
         <x:v>レイアウト崩れ・要素重なりが無い</x:v>
       </x:c>
       <x:c r="H144" s="5" t="str">
-        <x:v>未実施</x:v>
+        <x:v>合格</x:v>
       </x:c>
       <x:c r="I144" s="4" t="str">
-        <x:v>2026/06/17 section3 では Firefox の launchPersistentContext が起動直後に終了し、browserType.launchPersistentContext: Failed to launch the browser process で再実施不可。今回の整理では未実施(起動ブロッカー)として記録。evidence: _ff_launch_probe.mjs, 引き継ぎメモ</x:v>
+        <x:v>Firefox 既存証跡で 320/375/768/1024/1280/1920px の error.asp 表示を確認。レイアウト崩れ・要素重なりなし。evidence: A_error_WinFirefox_320.png / A_error_WinFirefox_375.png / A_error_WinFirefox_768.png / A_error_WinFirefox_1024.png / A_error_WinFirefox_1280.png / A_error_WinFirefox_1920.png</x:v>
       </x:c>
       <x:c r="J144" s="5" t="str">
         <x:v>Codex</x:v>
@@ -5736,10 +5736,10 @@
         <x:v>意図しない横スクロールが出ない</x:v>
       </x:c>
       <x:c r="H145" s="5" t="str">
-        <x:v>未実施</x:v>
+        <x:v>合格</x:v>
       </x:c>
       <x:c r="I145" s="4" t="str">
-        <x:v>2026/06/17 section3 では Firefox の launchPersistentContext が起動直後に終了し、browserType.launchPersistentContext: Failed to launch the browser process で再実施不可。今回の整理では未実施(起動ブロッカー)として記録。evidence: _ff_launch_probe.mjs, 引き継ぎメモ</x:v>
+        <x:v>Firefox 既存証跡で 320/375/768/1024/1280/1920px の error.asp を確認。意図しない横スクロールなし。evidence: A_error_WinFirefox_320.png / A_error_WinFirefox_375.png / A_error_WinFirefox_768.png / A_error_WinFirefox_1024.png / A_error_WinFirefox_1280.png / A_error_WinFirefox_1920.png</x:v>
       </x:c>
       <x:c r="J145" s="5" t="str">
         <x:v>Codex</x:v>
@@ -5771,10 +5771,10 @@
         <x:v>画像が画面幅を突き破らず縮小表示される</x:v>
       </x:c>
       <x:c r="H146" s="5" t="str">
-        <x:v>未実施</x:v>
+        <x:v>合格</x:v>
       </x:c>
       <x:c r="I146" s="4" t="str">
-        <x:v>2026/06/17 section3 では Firefox の launchPersistentContext が起動直後に終了し、browserType.launchPersistentContext: Failed to launch the browser process で再実施不可。今回の整理では未実施(起動ブロッカー)として記録。evidence: _ff_launch_probe.mjs, 引き継ぎメモ</x:v>
+        <x:v>Firefox 768px / 900px のヘッダー矩形確認で imageExceedsHeader=false。375px / 1280px の表示も問題なし。evidence: bugfix_metrics_20260615.json / A_error_WinFirefox_375.png / A_error_WinFirefox_1280.png</x:v>
       </x:c>
       <x:c r="J146" s="5" t="str">
         <x:v>Codex</x:v>
@@ -5806,10 +5806,10 @@
         <x:v>縦積み/横並びが破綻せずはみ出さない</x:v>
       </x:c>
       <x:c r="H147" s="5" t="str">
-        <x:v>未実施</x:v>
+        <x:v>合格</x:v>
       </x:c>
       <x:c r="I147" s="4" t="str">
-        <x:v>2026/06/17 section3 では Firefox の launchPersistentContext が起動直後に終了し、browserType.launchPersistentContext: Failed to launch the browser process で再実施不可。今回の整理では未実施(起動ブロッカー)として記録。evidence: _ff_launch_probe.mjs, 引き継ぎメモ</x:v>
+        <x:v>Firefox 375px / 1280px の error.asp で action-row のボタン配置に崩れなし。evidence: A_error_WinFirefox_375.png / A_error_WinFirefox_1280.png</x:v>
       </x:c>
       <x:c r="J147" s="5" t="str">
         <x:v>Codex</x:v>
@@ -5841,10 +5841,10 @@
         <x:v>最小44px相当で押し間違えない</x:v>
       </x:c>
       <x:c r="H148" s="5" t="str">
-        <x:v>未実施</x:v>
+        <x:v>保留</x:v>
       </x:c>
       <x:c r="I148" s="4" t="str">
-        <x:v>2026/06/17 section3 では Firefox の launchPersistentContext が起動直後に終了し、browserType.launchPersistentContext: Failed to launch the browser process で再実施不可。今回の整理では未実施(起動ブロッカー)として記録。evidence: _ff_launch_probe.mjs, 引き継ぎメモ</x:v>
+        <x:v>Firefox の error.asp について 44px 以上のタップターゲット実測証跡が不足しているため保留。既存スクリーンショットのみでは客先提出根拠として弱い。</x:v>
       </x:c>
       <x:c r="J148" s="5" t="str">
         <x:v>Codex</x:v>
@@ -5876,10 +5876,10 @@
         <x:v>回転後もレイアウト維持、破綻なし</x:v>
       </x:c>
       <x:c r="H149" s="5" t="str">
-        <x:v>未実施</x:v>
+        <x:v>合格</x:v>
       </x:c>
       <x:c r="I149" s="4" t="str">
-        <x:v>2026/06/17 section3 では Firefox の launchPersistentContext が起動直後に終了し、browserType.launchPersistentContext: Failed to launch the browser process で再実施不可。今回の整理では未実施(起動ブロッカー)として記録。evidence: _ff_launch_probe.mjs, 引き継ぎメモ</x:v>
+        <x:v>Firefox 回転証跡で 375x667 / 667x375 ともに error.asp のレイアウト維持を確認。evidence: A_error_WinFirefox_rotate_375x667.png / A_error_WinFirefox_rotate_667x375.png</x:v>
       </x:c>
       <x:c r="J149" s="5" t="str">
         <x:v>Codex</x:v>
@@ -5911,10 +5911,10 @@
         <x:v>テキスト読め重なり・見切れなし</x:v>
       </x:c>
       <x:c r="H150" s="5" t="str">
-        <x:v>未実施</x:v>
+        <x:v>合格</x:v>
       </x:c>
       <x:c r="I150" s="4" t="str">
-        <x:v>2026/06/17 section3 では Firefox の launchPersistentContext が起動直後に終了し、browserType.launchPersistentContext: Failed to launch the browser process で再実施不可。今回の整理では未実施(起動ブロッカー)として記録。evidence: _ff_launch_probe.mjs, 引き継ぎメモ</x:v>
+        <x:v>Firefox 200% zoom 証跡でテキストの重なり・見切れなし。evidence: A_error_WinFirefox_zoom200.png</x:v>
       </x:c>
       <x:c r="J150" s="5" t="str">
         <x:v>Codex</x:v>
@@ -5946,10 +5946,10 @@
         <x:v>文字化けなし(main.aspはCodePage欠落のため要確認)</x:v>
       </x:c>
       <x:c r="H151" s="5" t="str">
-        <x:v>未実施</x:v>
+        <x:v>合格</x:v>
       </x:c>
       <x:c r="I151" s="4" t="str">
-        <x:v>2026/06/17 section3 では Firefox の launchPersistentContext が起動直後に終了し、browserType.launchPersistentContext: Failed to launch the browser process で再実施不可。今回の整理では未実施(起動ブロッカー)として記録。evidence: _ff_launch_probe.mjs, 引き継ぎメモ</x:v>
+        <x:v>Firefox codepage 証跡で Shift_JIS 日本語表示に文字化けなし。evidence: A_error_WinFirefox_codepage_375.png</x:v>
       </x:c>
       <x:c r="J151" s="5" t="str">
         <x:v>Codex</x:v>
@@ -6051,10 +6051,10 @@
         <x:v>alt属性で内容が伝わる</x:v>
       </x:c>
       <x:c r="H154" s="5" t="str">
-        <x:v>未実施</x:v>
+        <x:v>合格</x:v>
       </x:c>
       <x:c r="I154" s="4" t="str">
-        <x:v>2026/06/17 section3 では Firefox の launchPersistentContext が起動直後に終了し、browserType.launchPersistentContext: Failed to launch the browser process で再実施不可。今回の整理では未実施(起動ブロッカー)として記録。evidence: _ff_launch_probe.mjs, 引き継ぎメモ</x:v>
+        <x:v>Firefox images disabled 証跡で alt テキスト表示を確認。evidence: A_error_WinFirefox_imagesDisabled_375.png</x:v>
       </x:c>
       <x:c r="J154" s="5" t="str">
         <x:v>Codex</x:v>
@@ -13423,28 +13423,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F5" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F5" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G5" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">index.asp?????????2????????????WEB???? / ????????????????evidence: C1_index_initial_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J5" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H5" s="4" t="str">
+        <x:v>index.asp で 2 コース（オンラインレッスン＆WEBセミナー / オンラインチャイナ）のラジオ一覧を表示確認。evidence: C1_index_initial_20260615.png</x:v>
+      </x:c>
+      <x:c r="I5" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J5" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -13473,28 +13467,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F6" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F6" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G6" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">??????????error.asp??????????????????????????????evidence: C1_04_after_timeout_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J6" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H6" s="4" t="str">
+        <x:v>コース未選択で次へ押下後、error.asp に「コースが選択されていません。」を表示確認。evidence: C1_04_after_timeout_20260615.png</x:v>
+      </x:c>
+      <x:c r="I6" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -13523,28 +13511,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F7" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F7" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G7" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">??????????WEB????????main.asp?????????????evidence: C1_05_to_main_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J7" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H7" s="4" t="str">
+        <x:v>オンラインレッスン＆WEBセミナー選択後、main.asp への遷移とセッション保持を確認。evidence: C1_05_to_main_20260615.png</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -13573,28 +13555,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F8" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Win Edge / 375・1280（一部コード検査）</x:t>
-        </x:is>
+      <x:c r="F8" s="5" t="str">
+        <x:v>Win Chrome popup / 375・1280</x:v>
       </x:c>
       <x:c r="G8" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">script-opened popup ? index.asp ?????????????? window.close() ? popup ??????? Chrome ??????evidence: C1_06_popup_before_close_chrome_20260617.png / chrome_c1_c2_probe_20260617.json</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H8" s="4" t="str">
+        <x:v>script-opened popup で index.asp を開き、閉じる押下で window.close() により popup が閉じることを Chrome 実機で確認。evidence: C1_06_popup_before_close_chrome_20260617.png / chrome_c1_c2_probe_20260617.json</x:v>
+      </x:c>
+      <x:c r="I8" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>2026/06/17</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -13639,28 +13615,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F10" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F10" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G10" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">???17??????select????????evidence: C1_05_to_main_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I10" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J10" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H10" s="4" t="str">
+        <x:v>残り 17 回の表示と学校 select の表示を確認。evidence: C1_05_to_main_20260615.png</x:v>
+      </x:c>
+      <x:c r="I10" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -13739,28 +13709,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F12" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F12" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G12" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">????????????error.asp?????????????????????????????????evidence: C2_03_no_school_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J12" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H12" s="4" t="str">
+        <x:v>学校未選択で予約操作後、error.asp に「学校名が選択されていないようです。」を表示確認。evidence: C2_03_no_school_20260615.png</x:v>
+      </x:c>
+      <x:c r="I12" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -13789,28 +13753,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F13" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F13" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G13" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">??????reserve.asp?School=5221?????????????evidence: C2_04_to_reserve_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J13" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H13" s="4" t="str">
+        <x:v>学校選択後、reserve.asp?School=5221 への遷移を確認。evidence: C2_04_to_reserve_20260615.png</x:v>
+      </x:c>
+      <x:c r="I13" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -13839,28 +13797,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F14" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F14" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G14" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">???main.asp??????????????selected?????????????evidence: C2_main_after_reserve_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J14" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H14" s="4" t="str">
+        <x:v>予約後に main.asp へ戻った際、ハオオンライン校が selected のまま保持されることを確認。evidence: C2_main_after_reserve_20260615.png</x:v>
+      </x:c>
+      <x:c r="I14" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -13889,28 +13841,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F15" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Win Edge / 375・1280（一部コード検査）</x:t>
-        </x:is>
+      <x:c r="F15" s="5" t="str">
+        <x:v>Win Chrome / 375・1280</x:v>
       </x:c>
       <x:c r="G15" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">未実施</x:t>
         </x:is>
       </x:c>
-      <x:c r="H15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CourseType=1 ? course 77 (?????????) ???current account uid=3070 ?? course 77 ??????????????? UI ?????course 61 ? CourseType=2 ??? C2-06 ?????evidence: index.asp radio value check / teacher_join_probe.asp?uid=3070&amp;course=77 / scenario_probe.asp?uid=3070&amp;course=77 / chrome_c1_c2_probe_20260617.json(61????)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J15" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H15" s="4" t="str">
+        <x:v>現行アカウントでは CourseType=1 の予約済み UI 証跡を取得できず未実施。course 77 は予約済み対象データがそろわず、course 61 は CourseType=2。evidence: C2_06_main_chrome_20260617.png / teacher_join_probe.asp / scenario_probe.asp / chrome_c1_c2_probe_20260617.json</x:v>
+      </x:c>
+      <x:c r="I15" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="str">
+        <x:v>2026/06/17</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -13939,28 +13885,20 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F16" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">不合格</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CourseType=2??????session_probe: ThisCourseType=2?????????????????????????????????????????????evidence: C2_main_after_reserve_20260615.png / runtime_regression_notes_20260615.txt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J16" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="F16" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
+      </x:c>
+      <x:c r="G16" s="5" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+      <x:c r="H16" s="4" t="str">
+        <x:v>CourseType=2 セッションでキャンセル一覧を表示したところ、時刻は出るが text_name / lesson_name は空欄だった。改修起因の不具合とは断定せず、対象マスタデータ不足による LEFT JOIN 結果空欄として保留扱い。evidence: C2_main_after_reserve_20260615.png / runtime_regression_notes_20260615.txt</x:v>
+      </x:c>
+      <x:c r="I16" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="str">
+        <x:v>2026/06/17</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -14039,28 +13977,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F18" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F18" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G18" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H18" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">???????????????error.asp????????????????????????????????????????evidence: C2_09_no_cancel_selection_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J18" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H18" s="4" t="str">
+        <x:v>キャンセル対象未選択で操作後、error.asp に「キャンセルするクラスが選択されていないようです。」を表示確認。evidence: C2_09_no_cancel_selection_20260615.png</x:v>
+      </x:c>
+      <x:c r="I18" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J18" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -14089,28 +14021,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F19" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F19" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G19" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H19" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12:00?12:50???????????????????16?17????????DB: cls_mirror_total 5?6, cls_total 5?6, les_count 1?0?evidence: C2_10_cancel_done_20260615.png / runtime_regression_notes_20260615.txt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J19" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H19" s="4" t="str">
+        <x:v>12:00〜12:50 をキャンセル後、残回数が 16→17 に戻ることと DB 値の復元を確認。evidence: C2_10_cancel_done_20260615.png / runtime_regression_notes_20260615.txt</x:v>
+      </x:c>
+      <x:c r="I19" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J19" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -14139,28 +14065,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F20" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F20" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G20" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H20" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CourseNumber=2????????????????session_probe????evidence: C1_05_to_main_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J20" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H20" s="4" t="str">
+        <x:v>CourseNumber=2 の条件で戻るボタン表示を確認。evidence: C1_05_to_main_20260615.png</x:v>
+      </x:c>
+      <x:c r="I20" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J20" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -14205,28 +14125,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F22" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F22" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G22" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H22" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">??reserve.asp??????????????????????evidence: C2_04_to_reserve_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I22" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J22" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H22" s="4" t="str">
+        <x:v>reserve.asp 初期表示で「日付を選択してください」を確認。evidence: C2_04_to_reserve_20260615.png</x:v>
+      </x:c>
+      <x:c r="I22" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J22" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -14255,28 +14169,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F23" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F23" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G23" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H23" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026?7?1??????/???????????????????evidence: C3_02_C3_06_july_no_class_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I23" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J23" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H23" s="4" t="str">
+        <x:v>2026/07/01 へ月送りし、July カレンダーの再描画を確認。evidence: C3_02_C3_06_july_no_class_20260615.png</x:v>
+      </x:c>
+      <x:c r="I23" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J23" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -14305,28 +14213,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F24" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F24" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G24" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H24" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6?29??????????????????????evidence: C3_03_click_date_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I24" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J24" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H24" s="4" t="str">
+        <x:v>2026/06/29 の日付選択後、その日のクラス一覧表示を確認。evidence: C3_03_click_date_20260615.png</x:v>
+      </x:c>
+      <x:c r="I24" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J24" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -14355,30 +14257,20 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F25" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Win Edge / 375・1280（一部コード検査）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G25" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">合格</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H25" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">calendar.jsで当日セルにcanowを付与する処理を確認。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I25" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J25" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026/06/08</x:t>
-        </x:is>
+      <x:c r="F25" s="5" t="str">
+        <x:v>Win Edge / 375・1280</x:v>
+      </x:c>
+      <x:c r="G25" s="5" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+      <x:c r="H25" s="4" t="str">
+        <x:v>calendar.js 上で canow 付与ロジックは確認したが、実画面の当日セル証跡が無いため保留。</x:v>
+      </x:c>
+      <x:c r="I25" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J25" s="5" t="str">
+        <x:v>2026/06/17</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -14407,30 +14299,20 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F26" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Win Edge / 375・1280（一部コード検査）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G26" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">合格</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H26" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">calendar.jsのうるう年判定は4/100/400年ルールで実装済み。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I26" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J26" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026/06/08</x:t>
-        </x:is>
+      <x:c r="F26" s="5" t="str">
+        <x:v>Win Edge / 375・1280</x:v>
+      </x:c>
+      <x:c r="G26" s="5" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+      <x:c r="H26" s="4" t="str">
+        <x:v>calendar.js 上でうるう年判定ロジックは確認したが、2/29 の実画面証跡が無いため保留。</x:v>
+      </x:c>
+      <x:c r="I26" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J26" s="5" t="str">
+        <x:v>2026/06/17</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -14459,28 +14341,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F27" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F27" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G27" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H27" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026?7?1??????????????????????????????evidence: C3_02_C3_06_july_no_class_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I27" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J27" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H27" s="4" t="str">
+        <x:v>2026/07/01 で「該当日の開講予定クラスはありません。」を確認。evidence: C3_02_C3_06_july_no_class_20260615.png</x:v>
+      </x:c>
+      <x:c r="I27" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J27" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -14509,28 +14385,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F28" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F28" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G28" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H28" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026?6?29? 12:00?12:50 ?????????????????????????evidence: C3_03_click_date_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I28" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J28" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H28" s="4" t="str">
+        <x:v>2026/06/29 12:00〜12:50 が「予約可能」でラジオ有効であることを確認。evidence: C3_03_click_date_20260615.png</x:v>
+      </x:c>
+      <x:c r="I28" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J28" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -14659,28 +14529,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F31" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F31" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G31" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H31" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026?6?29? 14:00?14:50 ????????????????????????evidence: C3_03_click_date_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I31" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J31" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H31" s="4" t="str">
+        <x:v>2026/06/29 14:00〜14:50 が「予約済」でラジオ無効であることを確認。evidence: C3_03_click_date_20260615.png</x:v>
+      </x:c>
+      <x:c r="I31" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J31" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -14759,28 +14623,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F33" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F33" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G33" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H33" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">????????????error.asp?????????????????????????????????????evidence: C3_12_no_reserve_selection_20260615.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I33" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J33" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H33" s="4" t="str">
+        <x:v>予約対象未選択で操作後、error.asp に「予約するクラスが選択されていないようです。」を表示確認。evidence: C3_12_no_reserve_selection_20260615.png</x:v>
+      </x:c>
+      <x:c r="I33" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J33" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -14809,28 +14667,22 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F34" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex IAB ??</x:t>
-        </x:is>
+      <x:c r="F34" s="5" t="str">
+        <x:v>Codex IAB / 375・1280</x:v>
       </x:c>
       <x:c r="G34" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">合格</x:t>
         </x:is>
       </x:c>
-      <x:c r="H34" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12:00?12:50????????????????????????????????????DB: cls_mirror_total 6?5, cls_total 6?5, les_count 0?1?evidence: C3_13_reserved_20260615.png / runtime_regression_notes_20260615.txt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I34" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J34" s="14" t="n">
-        <x:v>46190</x:v>
+      <x:c r="H34" s="4" t="str">
+        <x:v>12:00〜12:50 を予約後、成功メッセージ表示と DB 値変化を確認。evidence: C3_13_reserved_20260615.png / runtime_regression_notes_20260615.txt</x:v>
+      </x:c>
+      <x:c r="I34" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J34" s="14" t="str">
+        <x:v>2026/06/15</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -14859,30 +14711,20 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F35" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Win Edge / 375・1280（一部コード検査）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G35" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">合格</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H35" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reserve.aspの主要出力はChkSecXss経由、テーブル状態出力もクラス値を固定文字列で制御していることを確認。特殊文字入り実データは未実施。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I35" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J35" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026/06/08</x:t>
-        </x:is>
+      <x:c r="F35" s="5" t="str">
+        <x:v>Win Edge / 375・1280</x:v>
+      </x:c>
+      <x:c r="G35" s="5" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="str">
+        <x:v>ChkSecXss 経由のコード確認はできたが、特殊文字を含む実データ表示証跡が無いため保留。</x:v>
+      </x:c>
+      <x:c r="I35" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J35" s="5" t="str">
+        <x:v>2026/06/17</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -14927,30 +14769,20 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F37" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Win Edge / 375・1280（一部コード検査）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G37" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">合格</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H37" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">error.asp?Message=テスト&lt;br&gt;2行目 をEdge headlessで表示確認。&lt;br&gt;は文字列ではなく改行として表示。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I37" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J37" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026/06/08</x:t>
-        </x:is>
+      <x:c r="F37" s="5" t="str">
+        <x:v>Win Edge / 375・1280</x:v>
+      </x:c>
+      <x:c r="G37" s="5" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+      <x:c r="H37" s="4" t="str">
+        <x:v>error.asp?Message=... の表示確認メモはあるが、提出用スクリーンショット証跡が残っていないため保留。</x:v>
+      </x:c>
+      <x:c r="I37" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J37" s="5" t="str">
+        <x:v>2026/06/17</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -14979,30 +14811,20 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="F38" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Win Edge / 375・1280（一部コード検査）</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G38" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">合格</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H38" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">error.aspの「戻る」はhistory.back、「閉じる」はwindow.closeをコード確認。Edge表示でボタン描画を確認。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I38" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J38" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026/06/08</x:t>
-        </x:is>
+      <x:c r="F38" s="5" t="str">
+        <x:v>Win Edge / 375・1280</x:v>
+      </x:c>
+      <x:c r="G38" s="5" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+      <x:c r="H38" s="4" t="str">
+        <x:v>error.asp の戻る/閉じるのコード確認はあるが、提出用の操作証跡が無いため保留。</x:v>
+      </x:c>
+      <x:c r="I38" s="5" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="J38" s="5" t="str">
+        <x:v>2026/06/17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15624,10 +15446,8 @@
           <x:t xml:space="preserve">375 / 1280</x:t>
         </x:is>
       </x:c>
-      <x:c r="E32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CourseType=2 のキャンセル一覧で text_name / lesson_name が空になる。改修起因ではなく、対象データ不足により LEFT JOIN 結果が NULL/空文字になっている。</x:t>
-        </x:is>
+      <x:c r="E32" t="str">
+        <x:v>CourseType=2 のキャンセル一覧で text_name / lesson_name が空になる。改修起因ではなく、対象データ不足により LEFT JOIN 結果が NULL/空欄になっている。</x:v>
       </x:c>
       <x:c r="F32" t="inlineStr">
         <x:is>
@@ -15639,20 +15459,14 @@
           <x:t xml:space="preserve">2026/06/15</x:t>
         </x:is>
       </x:c>
-      <x:c r="H32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">データ不足</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">コード回帰ではなくデータ不足と切り分け済み。修正対象外。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026/06/15 原因切り分け完了。元版でも同系統の JOIN 構造、対象データは text_name / lesson_name 空。</x:t>
-        </x:is>
+      <x:c r="H32" t="str">
+        <x:v>データ不足</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>コード回帰ではなくデータ不足と切り分け済み。修正対象外。C2-07 は保留扱い。</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>2026/06/15 原因切り分け完了。元版でも同系統の JOIN 構造で、対象データは text_name / lesson_name が空欄。evidence: C2_main_after_reserve_20260615.png / runtime_regression_notes_20260615.txt</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
